--- a/组合实盘追踪/20260601_银河.xlsx
+++ b/组合实盘追踪/20260601_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>673.6</v>
+        <v>678.6</v>
       </c>
       <c r="D2" s="1">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2">
-        <v>-0.0044</v>
+        <v>0.003</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-37.5</v>
+        <v>-32.5</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0527</v>
+        <v>-0.0457</v>
       </c>
       <c r="L2" s="1">
-        <v>-37.5</v>
+        <v>-32.5</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0527</v>
+        <v>-0.0457</v>
       </c>
       <c r="N2" s="1">
-        <v>-23.6</v>
+        <v>-18.8</v>
       </c>
       <c r="O2" s="1">
-        <v>-23.6</v>
+        <v>-18.8</v>
       </c>
       <c r="P2" s="1">
-        <v>-37.5</v>
+        <v>-32.7</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0232</v>
+        <v>0.0233</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>16</v>
       </c>
       <c r="T2" s="2">
-        <v>-0.0044</v>
+        <v>0.003</v>
       </c>
       <c r="U2" s="5">
-        <v>3.368</v>
+        <v>3.393</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0558</v>
+        <v>0.048</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0017</v>
+        <v>0.0092</v>
       </c>
       <c r="Y2" s="2">
-        <v>-0.0184</v>
+        <v>-0.0111</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1493</v>
+        <v>0.1578</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4073</v>
+        <v>0.4178</v>
       </c>
     </row>
     <row r="3">
@@ -648,16 +648,16 @@
         <v>-0.04</v>
       </c>
       <c r="N3" s="1">
-        <v>-9.6</v>
+        <v>-8.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-9.6</v>
+        <v>-9.2</v>
       </c>
       <c r="P3" s="1">
-        <v>-34.5</v>
+        <v>-34.1</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0285</v>
+        <v>0.0284</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>700.7</v>
+        <v>710.6</v>
       </c>
       <c r="D4" s="1">
-        <v>-2.2</v>
+        <v>7.7</v>
       </c>
       <c r="E4" s="2">
-        <v>-0.0031</v>
+        <v>0.011</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-36.4</v>
+        <v>-26.5</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0494</v>
+        <v>-0.036</v>
       </c>
       <c r="L4" s="1">
-        <v>-36.4</v>
+        <v>-26.5</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0494</v>
+        <v>-0.036</v>
       </c>
       <c r="N4" s="1">
-        <v>-5.5</v>
+        <v>4.4</v>
       </c>
       <c r="O4" s="1">
-        <v>-5.5</v>
+        <v>4.4</v>
       </c>
       <c r="P4" s="1">
-        <v>-36.4</v>
+        <v>-26.5</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0241</v>
+        <v>0.0244</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>16</v>
       </c>
       <c r="T4" s="2">
-        <v>-0.0031</v>
+        <v>0.011</v>
       </c>
       <c r="U4" s="5">
-        <v>0.637</v>
+        <v>0.646</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0518</v>
+        <v>0.0372</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0124</v>
+        <v>0.0016</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0701</v>
+        <v>-0.057</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1749</v>
+        <v>-0.1632</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1066</v>
+        <v>-0.094</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>984.6</v>
+        <v>985</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E5" s="2">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-6.7</v>
+        <v>-6.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0068</v>
+        <v>-0.0064</v>
       </c>
       <c r="L5" s="1">
-        <v>-6.7</v>
+        <v>-6.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0068</v>
+        <v>-0.0064</v>
       </c>
       <c r="N5" s="1">
-        <v>-6.4</v>
+        <v>-6</v>
       </c>
       <c r="O5" s="1">
-        <v>-6.4</v>
+        <v>-6.2</v>
       </c>
       <c r="P5" s="1">
-        <v>-6.7</v>
+        <v>-6.5</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0339</v>
+        <v>0.0338</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>16</v>
       </c>
       <c r="T5" s="2">
-        <v>0</v>
+        <v>0.0004</v>
       </c>
       <c r="U5" s="5">
-        <v>4.923</v>
+        <v>4.925</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0069</v>
+        <v>0.0065</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0205</v>
+        <v>0.0209</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0419</v>
+        <v>0.0423</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0897</v>
+        <v>0.0901</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3046</v>
+        <v>0.3051</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>939.8</v>
+        <v>940.5</v>
       </c>
       <c r="D6" s="1">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0001</v>
+        <v>0.0009</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-33.9</v>
+        <v>-33.2</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0348</v>
+        <v>-0.0341</v>
       </c>
       <c r="L6" s="1">
-        <v>-33.9</v>
+        <v>-33.2</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0348</v>
+        <v>-0.0341</v>
       </c>
       <c r="N6" s="1">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="O6" s="1">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="P6" s="1">
-        <v>-35.7</v>
+        <v>-33.3</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0324</v>
+        <v>0.0323</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>16</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0001</v>
+        <v>0.0009</v>
       </c>
       <c r="U6" s="5">
-        <v>9.398</v>
+        <v>9.405</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0361</v>
+        <v>0.0353</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0289</v>
+        <v>-0.0282</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1404</v>
+        <v>-0.1398</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0365</v>
+        <v>0.0373</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2753</v>
+        <v>0.2763</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3026.7</v>
+        <v>3032.1</v>
       </c>
       <c r="D7" s="1">
-        <v>-2.7</v>
+        <v>2.7</v>
       </c>
       <c r="E7" s="2">
-        <v>-0.0009</v>
+        <v>0.0009</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,28 +968,28 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0026</v>
+        <v>0.0044</v>
       </c>
       <c r="L7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0026</v>
+        <v>0.0044</v>
       </c>
       <c r="N7" s="1">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="P7" s="1">
-        <v>7.95</v>
+        <v>13.35</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1042</v>
+        <v>0.104</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>16</v>
       </c>
       <c r="T7" s="2">
-        <v>-0.0009</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.121</v>
+        <v>1.123</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0036</v>
+        <v>0.0054</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0117</v>
+        <v>0.0135</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0145</v>
+        <v>0.0163</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0216</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>809.4</v>
+        <v>817.4</v>
       </c>
       <c r="D8" s="1">
-        <v>-1.2</v>
+        <v>6.8</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0015</v>
+        <v>0.0084</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>22.7</v>
+        <v>30.7</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0289</v>
+        <v>0.039</v>
       </c>
       <c r="L8" s="1">
-        <v>22.7</v>
+        <v>30.7</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0289</v>
+        <v>0.039</v>
       </c>
       <c r="N8" s="1">
-        <v>-23</v>
+        <v>-14.6</v>
       </c>
       <c r="O8" s="1">
-        <v>-23</v>
+        <v>-14.4</v>
       </c>
       <c r="P8" s="1">
-        <v>22.7</v>
+        <v>31.3</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0279</v>
+        <v>0.028</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>16</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0015</v>
+        <v>0.0084</v>
       </c>
       <c r="U8" s="5">
-        <v>4.047</v>
+        <v>4.087</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0971</v>
+        <v>0.1079</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.226</v>
+        <v>0.2381</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3334</v>
+        <v>0.3466</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0523</v>
+        <v>1.0725</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19584.6</v>
+        <v>19658.8</v>
       </c>
       <c r="D9" s="1">
-        <v>-15.4</v>
+        <v>58.8</v>
       </c>
       <c r="E9" s="2">
-        <v>-0.0008</v>
+        <v>0.003</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,25 +1134,25 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-793.04</v>
+        <v>-718.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0389</v>
+        <v>-0.0353</v>
       </c>
       <c r="L9" s="1">
-        <v>-793.04</v>
+        <v>-718.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0389</v>
+        <v>-0.0353</v>
       </c>
       <c r="N9" s="1">
-        <v>-217</v>
+        <v>-121.8</v>
       </c>
       <c r="O9" s="1">
-        <v>-217</v>
+        <v>-145.6</v>
       </c>
       <c r="P9" s="1">
-        <v>-793.04</v>
+        <v>-721.64</v>
       </c>
       <c r="Q9" s="2">
         <v>0.6742</v>
@@ -1164,28 +1164,28 @@
         <v>16</v>
       </c>
       <c r="T9" s="2">
-        <v>-0.0008</v>
+        <v>0.003</v>
       </c>
       <c r="U9" s="5">
-        <v>13.989</v>
+        <v>14.042</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0405</v>
+        <v>0.0365</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0213</v>
+        <v>-0.0176</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0416</v>
+        <v>-0.0379</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0448</v>
+        <v>0.0487</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1645</v>
+        <v>0.1689</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>640.8</v>
+        <v>645.2</v>
       </c>
       <c r="D10" s="1">
-        <v>6.8</v>
+        <v>11.2</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0107</v>
+        <v>0.0177</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-31.3</v>
+        <v>-26.9</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0466</v>
+        <v>-0.04</v>
       </c>
       <c r="L10" s="1">
-        <v>-31.3</v>
+        <v>-26.9</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0466</v>
+        <v>-0.04</v>
       </c>
       <c r="N10" s="1">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="O10" s="1">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="P10" s="1">
-        <v>-31.3</v>
+        <v>-26.9</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0221</v>
@@ -1247,28 +1247,28 @@
         <v>16</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0107</v>
+        <v>0.0177</v>
       </c>
       <c r="U10" s="5">
-        <v>1.602</v>
+        <v>1.613</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0487</v>
+        <v>0.0415</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.0713</v>
+        <v>-0.065</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2535</v>
+        <v>0.2621</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.2982</v>
+        <v>0.3071</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2496</v>
+        <v>0.2581</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>859.2</v>
+        <v>860.4</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E11" s="2">
-        <v>-0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0015</v>
+        <v>-0.0001</v>
       </c>
       <c r="L11" s="1">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0015</v>
+        <v>-0.0001</v>
       </c>
       <c r="N11" s="1">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="O11" s="1">
-        <v>-4</v>
+        <v>-2.8</v>
       </c>
       <c r="P11" s="1">
-        <v>-1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.0296</v>
+        <v>0.0295</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,28 +1330,28 @@
         <v>16</v>
       </c>
       <c r="T11" s="2">
-        <v>-0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="U11" s="5">
-        <v>2.148</v>
+        <v>2.151</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0014</v>
+        <v/>
       </c>
       <c r="X11" s="2">
-        <v>0.0302</v>
+        <v>0.0317</v>
       </c>
       <c r="Y11" s="2">
-        <v>-0.0079</v>
+        <v>-0.0065</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.179</v>
+        <v>0.1806</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2955</v>
+        <v>0.2973</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29047.8</v>
+        <v>29157</v>
       </c>
       <c r="D12" s="1">
-        <v>-20.4</v>
+        <v>88.8</v>
       </c>
       <c r="E12" s="2">
-        <v>-0.0007</v>
+        <v>0.0031</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-943.99</v>
+        <v>-834.79</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0315</v>
+        <v>-0.0278</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-285.4</v>
+        <v>-153.5</v>
       </c>
       <c r="O12" s="1">
-        <v>-287.2</v>
+        <v>-178.5</v>
       </c>
       <c r="P12" s="1">
-        <v>-945.79</v>
+        <v>-837.09</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>

--- a/组合实盘追踪/20260601_银河.xlsx
+++ b/组合实盘追踪/20260601_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>678.6</v>
+        <v>680.2</v>
       </c>
       <c r="D2" s="1">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.003</v>
+        <v>0.0053</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-32.5</v>
+        <v>-30.9</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0457</v>
+        <v>-0.0434</v>
       </c>
       <c r="L2" s="1">
-        <v>-32.5</v>
+        <v>-30.9</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0457</v>
+        <v>-0.0434</v>
       </c>
       <c r="N2" s="1">
-        <v>-18.8</v>
+        <v>-18</v>
       </c>
       <c r="O2" s="1">
-        <v>-18.8</v>
+        <v>-16.6</v>
       </c>
       <c r="P2" s="1">
-        <v>-32.7</v>
+        <v>-30.5</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0233</v>
@@ -583,28 +583,28 @@
         <v>16</v>
       </c>
       <c r="T2" s="2">
-        <v>0.003</v>
+        <v>0.0053</v>
       </c>
       <c r="U2" s="5">
-        <v>3.393</v>
+        <v>3.401</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.048</v>
+        <v>0.0456</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0092</v>
+        <v>0.0116</v>
       </c>
       <c r="Y2" s="2">
-        <v>-0.0111</v>
+        <v>-0.0088</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1578</v>
+        <v>0.1605</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4178</v>
+        <v>0.4211</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>828.4</v>
+        <v>827.2</v>
       </c>
       <c r="D3" s="1">
-        <v>-2.4</v>
+        <v>-3.6</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0029</v>
+        <v>-0.0043</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,25 +636,25 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-34.5</v>
+        <v>-35.7</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.04</v>
+        <v>-0.0414</v>
       </c>
       <c r="L3" s="1">
-        <v>-34.5</v>
+        <v>-35.7</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.04</v>
+        <v>-0.0414</v>
       </c>
       <c r="N3" s="1">
-        <v>-8.8</v>
+        <v>-10.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-9.2</v>
+        <v>-10.4</v>
       </c>
       <c r="P3" s="1">
-        <v>-34.1</v>
+        <v>-35.3</v>
       </c>
       <c r="Q3" s="2">
         <v>0.0284</v>
@@ -666,28 +666,28 @@
         <v>16</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0029</v>
+        <v>-0.0043</v>
       </c>
       <c r="U3" s="5">
-        <v>2.071</v>
+        <v>2.068</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0415</v>
+        <v>0.043</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0421</v>
+        <v>-0.0435</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0267</v>
+        <v>0.0252</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0232</v>
+        <v>0.0218</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0753</v>
+        <v>0.0737</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>710.6</v>
+        <v>715</v>
       </c>
       <c r="D4" s="1">
-        <v>7.7</v>
+        <v>12.1</v>
       </c>
       <c r="E4" s="2">
-        <v>0.011</v>
+        <v>0.0172</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-26.5</v>
+        <v>-22.1</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.036</v>
+        <v>-0.03</v>
       </c>
       <c r="L4" s="1">
-        <v>-26.5</v>
+        <v>-22.1</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.036</v>
+        <v>-0.03</v>
       </c>
       <c r="N4" s="1">
-        <v>4.4</v>
+        <v>8.8</v>
       </c>
       <c r="O4" s="1">
-        <v>4.4</v>
+        <v>8.8</v>
       </c>
       <c r="P4" s="1">
-        <v>-26.5</v>
+        <v>-22.1</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0244</v>
+        <v>0.0245</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>16</v>
       </c>
       <c r="T4" s="2">
-        <v>0.011</v>
+        <v>0.0172</v>
       </c>
       <c r="U4" s="5">
-        <v>0.646</v>
+        <v>0.65</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0372</v>
+        <v>0.0308</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0016</v>
+        <v>0.0078</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.057</v>
+        <v>-0.0511</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1632</v>
+        <v>-0.1581</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.094</v>
+        <v>-0.0884</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D5" s="1">
-        <v>0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="E5" s="2">
-        <v>0.0004</v>
+        <v>-0.0006</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,25 +802,25 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-6.3</v>
+        <v>-7.3</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0064</v>
+        <v>-0.0074</v>
       </c>
       <c r="L5" s="1">
-        <v>-6.3</v>
+        <v>-7.3</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0064</v>
+        <v>-0.0074</v>
       </c>
       <c r="N5" s="1">
-        <v>-6</v>
+        <v>-6.8</v>
       </c>
       <c r="O5" s="1">
-        <v>-6.2</v>
+        <v>-7</v>
       </c>
       <c r="P5" s="1">
-        <v>-6.5</v>
+        <v>-7.3</v>
       </c>
       <c r="Q5" s="2">
         <v>0.0338</v>
@@ -832,28 +832,28 @@
         <v>16</v>
       </c>
       <c r="T5" s="2">
-        <v>0.0004</v>
+        <v>-0.0006</v>
       </c>
       <c r="U5" s="5">
-        <v>4.925</v>
+        <v>4.92</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0065</v>
+        <v>0.0075</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0209</v>
+        <v>0.0199</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0423</v>
+        <v>0.0413</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0901</v>
+        <v>0.089</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3051</v>
+        <v>0.3038</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>940.5</v>
+        <v>940.3</v>
       </c>
       <c r="D6" s="1">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0009</v>
+        <v>0.0006</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,19 +885,19 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-33.2</v>
+        <v>-33.4</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0341</v>
+        <v>-0.0343</v>
       </c>
       <c r="L6" s="1">
-        <v>-33.2</v>
+        <v>-33.4</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0341</v>
+        <v>-0.0343</v>
       </c>
       <c r="N6" s="1">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O6" s="1">
         <v>4.1</v>
@@ -915,28 +915,28 @@
         <v>16</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0009</v>
+        <v>0.0006</v>
       </c>
       <c r="U6" s="5">
-        <v>9.405</v>
+        <v>9.403</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0353</v>
+        <v>0.0355</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0282</v>
+        <v>-0.0284</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.1398</v>
+        <v>-0.14</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0373</v>
+        <v>0.0371</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.2763</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3032.1</v>
+        <v>3029.4</v>
       </c>
       <c r="D7" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>0.0009</v>
+        <v>0</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,25 +968,25 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>13.35</v>
+        <v>10.65</v>
       </c>
       <c r="K7" s="2">
-        <v>0.0044</v>
+        <v>0.0035</v>
       </c>
       <c r="L7" s="1">
-        <v>13.35</v>
+        <v>10.65</v>
       </c>
       <c r="M7" s="2">
-        <v>0.0044</v>
+        <v>0.0035</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="O7" s="1">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="P7" s="1">
-        <v>13.35</v>
+        <v>10.65</v>
       </c>
       <c r="Q7" s="2">
         <v>0.104</v>
@@ -998,10 +998,10 @@
         <v>16</v>
       </c>
       <c r="T7" s="2">
-        <v>0.0009</v>
+        <v>0</v>
       </c>
       <c r="U7" s="5">
-        <v>1.123</v>
+        <v>1.122</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0054</v>
+        <v>0.0045</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0135</v>
+        <v>0.0126</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0163</v>
+        <v>0.0154</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0234</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>817.4</v>
+        <v>809.6</v>
       </c>
       <c r="D8" s="1">
-        <v>6.8</v>
+        <v>-1</v>
       </c>
       <c r="E8" s="2">
-        <v>0.0084</v>
+        <v>-0.0012</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>30.7</v>
+        <v>22.9</v>
       </c>
       <c r="K8" s="2">
-        <v>0.039</v>
+        <v>0.0291</v>
       </c>
       <c r="L8" s="1">
-        <v>30.7</v>
+        <v>22.9</v>
       </c>
       <c r="M8" s="2">
-        <v>0.039</v>
+        <v>0.0291</v>
       </c>
       <c r="N8" s="1">
-        <v>-14.6</v>
+        <v>-23</v>
       </c>
       <c r="O8" s="1">
-        <v>-14.4</v>
+        <v>-22.8</v>
       </c>
       <c r="P8" s="1">
-        <v>31.3</v>
+        <v>22.9</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.028</v>
+        <v>0.0278</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>16</v>
       </c>
       <c r="T8" s="2">
-        <v>0.0084</v>
+        <v>-0.0012</v>
       </c>
       <c r="U8" s="5">
-        <v>4.087</v>
+        <v>4.048</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.1079</v>
+        <v>0.0973</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2381</v>
+        <v>0.2263</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3466</v>
+        <v>0.3338</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0725</v>
+        <v>1.0528</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19658.8</v>
+        <v>19651.8</v>
       </c>
       <c r="D9" s="1">
-        <v>58.8</v>
+        <v>51.8</v>
       </c>
       <c r="E9" s="2">
-        <v>0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-718.84</v>
+        <v>-725.84</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0353</v>
+        <v>-0.0356</v>
       </c>
       <c r="L9" s="1">
-        <v>-718.84</v>
+        <v>-725.84</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0353</v>
+        <v>-0.0356</v>
       </c>
       <c r="N9" s="1">
-        <v>-121.8</v>
+        <v>-137.2</v>
       </c>
       <c r="O9" s="1">
-        <v>-145.6</v>
+        <v>-149.8</v>
       </c>
       <c r="P9" s="1">
-        <v>-721.64</v>
+        <v>-725.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6742</v>
+        <v>0.6743</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>16</v>
       </c>
       <c r="T9" s="2">
-        <v>0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="U9" s="5">
-        <v>14.042</v>
+        <v>14.037</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0365</v>
+        <v>0.0369</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0176</v>
+        <v>-0.0179</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0379</v>
+        <v>-0.0383</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0487</v>
+        <v>0.0484</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1689</v>
+        <v>0.1685</v>
       </c>
     </row>
     <row r="10">
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>645.2</v>
+        <v>644.4</v>
       </c>
       <c r="D10" s="1">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0177</v>
+        <v>0.0164</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,25 +1217,25 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-26.9</v>
+        <v>-27.7</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.04</v>
+        <v>-0.0412</v>
       </c>
       <c r="L10" s="1">
-        <v>-26.9</v>
+        <v>-27.7</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.04</v>
+        <v>-0.0412</v>
       </c>
       <c r="N10" s="1">
-        <v>10</v>
+        <v>9.2</v>
       </c>
       <c r="O10" s="1">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="P10" s="1">
-        <v>-26.9</v>
+        <v>-27.3</v>
       </c>
       <c r="Q10" s="2">
         <v>0.0221</v>
@@ -1247,28 +1247,28 @@
         <v>16</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0177</v>
+        <v>0.0164</v>
       </c>
       <c r="U10" s="5">
-        <v>1.613</v>
+        <v>1.611</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0415</v>
+        <v>0.0428</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.065</v>
+        <v>-0.0661</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2621</v>
+        <v>0.2605</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3071</v>
+        <v>0.3055</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2581</v>
+        <v>0.2566</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>860.4</v>
+        <v>860</v>
       </c>
       <c r="D11" s="1">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0001</v>
+        <v>-0.0006</v>
       </c>
       <c r="L11" s="1">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0001</v>
+        <v>-0.0006</v>
       </c>
       <c r="N11" s="1">
-        <v>-2</v>
+        <v>-2.4</v>
       </c>
       <c r="O11" s="1">
-        <v>-2.8</v>
+        <v>-2.4</v>
       </c>
       <c r="P11" s="1">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0295</v>
@@ -1330,28 +1330,28 @@
         <v>16</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0009</v>
+        <v>0.0005</v>
       </c>
       <c r="U11" s="5">
-        <v>2.151</v>
+        <v>2.15</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v/>
+        <v>0.0005</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0317</v>
+        <v>0.0312</v>
       </c>
       <c r="Y11" s="2">
-        <v>-0.0065</v>
+        <v>-0.0069</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1806</v>
+        <v>0.18</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2973</v>
+        <v>0.2967</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29157</v>
+        <v>29141.9</v>
       </c>
       <c r="D12" s="1">
-        <v>88.8</v>
+        <v>73.7</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0031</v>
+        <v>0.0025</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-834.79</v>
+        <v>-849.89</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0278</v>
+        <v>-0.0283</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-153.5</v>
+        <v>-178.9</v>
       </c>
       <c r="O12" s="1">
-        <v>-178.5</v>
+        <v>-189.2</v>
       </c>
       <c r="P12" s="1">
-        <v>-837.09</v>
+        <v>-847.79</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>

--- a/组合实盘追踪/20260601_银河.xlsx
+++ b/组合实盘追踪/20260601_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>680.2</v>
+        <v>671.8</v>
       </c>
       <c r="D2" s="1">
-        <v>3.6</v>
+        <v>-4.8</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0053</v>
+        <v>-0.0071</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,28 +553,28 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-30.9</v>
+        <v>-39.3</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0434</v>
+        <v>-0.0553</v>
       </c>
       <c r="L2" s="1">
-        <v>-30.9</v>
+        <v>-39.3</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0434</v>
+        <v>-0.0553</v>
       </c>
       <c r="N2" s="1">
-        <v>-18</v>
+        <v>-25.4</v>
       </c>
       <c r="O2" s="1">
-        <v>-16.6</v>
+        <v>-25.4</v>
       </c>
       <c r="P2" s="1">
-        <v>-30.5</v>
+        <v>-39.3</v>
       </c>
       <c r="Q2" s="2">
-        <v>0.0233</v>
+        <v>0.0231</v>
       </c>
       <c r="R2" s="3">
         <v>200</v>
@@ -583,28 +583,28 @@
         <v>16</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0053</v>
+        <v>-0.0071</v>
       </c>
       <c r="U2" s="5">
-        <v>3.401</v>
+        <v>3.359</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0456</v>
+        <v>0.0586</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0116</v>
+        <v>-0.0009</v>
       </c>
       <c r="Y2" s="2">
-        <v>-0.0088</v>
+        <v>-0.021</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1605</v>
+        <v>0.1462</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.4211</v>
+        <v>0.4036</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>827.2</v>
+        <v>829.2</v>
       </c>
       <c r="D3" s="1">
-        <v>-3.6</v>
+        <v>-1.6</v>
       </c>
       <c r="E3" s="2">
-        <v>-0.0043</v>
+        <v>-0.0019</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-35.7</v>
+        <v>-33.7</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0414</v>
+        <v>-0.0391</v>
       </c>
       <c r="L3" s="1">
-        <v>-35.7</v>
+        <v>-33.7</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0414</v>
+        <v>-0.0391</v>
       </c>
       <c r="N3" s="1">
-        <v>-10.8</v>
+        <v>-8.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-10.4</v>
+        <v>-8.8</v>
       </c>
       <c r="P3" s="1">
-        <v>-35.3</v>
+        <v>-33.7</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0284</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>16</v>
       </c>
       <c r="T3" s="2">
-        <v>-0.0043</v>
+        <v>-0.0019</v>
       </c>
       <c r="U3" s="5">
-        <v>2.068</v>
+        <v>2.073</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.043</v>
+        <v>0.0405</v>
       </c>
       <c r="X3" s="2">
-        <v>-0.0435</v>
+        <v>-0.0412</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.0252</v>
+        <v>0.0277</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0218</v>
+        <v>0.0242</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.0737</v>
+        <v>0.0763</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>715</v>
+        <v>712.8</v>
       </c>
       <c r="D4" s="1">
-        <v>12.1</v>
+        <v>9.9</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0172</v>
+        <v>0.0141</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,25 +719,25 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-22.1</v>
+        <v>-24.3</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.03</v>
+        <v>-0.033</v>
       </c>
       <c r="L4" s="1">
-        <v>-22.1</v>
+        <v>-24.3</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.03</v>
+        <v>-0.033</v>
       </c>
       <c r="N4" s="1">
-        <v>8.8</v>
+        <v>6.6</v>
       </c>
       <c r="O4" s="1">
-        <v>8.8</v>
+        <v>6.6</v>
       </c>
       <c r="P4" s="1">
-        <v>-22.1</v>
+        <v>-24.3</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0245</v>
@@ -749,28 +749,28 @@
         <v>16</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0172</v>
+        <v>0.0141</v>
       </c>
       <c r="U4" s="5">
-        <v>0.65</v>
+        <v>0.648</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0308</v>
+        <v>0.034</v>
       </c>
       <c r="X4" s="2">
-        <v>0.0078</v>
+        <v>0.0047</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.0511</v>
+        <v>-0.0541</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1581</v>
+        <v>-0.1606</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.0884</v>
+        <v>-0.0912</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>984</v>
+        <v>973.6</v>
       </c>
       <c r="D5" s="1">
-        <v>-0.6</v>
+        <v>-11</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0006</v>
+        <v>-0.0112</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-7.3</v>
+        <v>-17.7</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0074</v>
+        <v>-0.0179</v>
       </c>
       <c r="L5" s="1">
-        <v>-7.3</v>
+        <v>-17.7</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0074</v>
+        <v>-0.0179</v>
       </c>
       <c r="N5" s="1">
-        <v>-6.8</v>
+        <v>-17.4</v>
       </c>
       <c r="O5" s="1">
-        <v>-7</v>
+        <v>-17.4</v>
       </c>
       <c r="P5" s="1">
-        <v>-7.3</v>
+        <v>-17.7</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0338</v>
+        <v>0.0335</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>16</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0006</v>
+        <v>-0.0112</v>
       </c>
       <c r="U5" s="5">
-        <v>4.92</v>
+        <v>4.868</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0075</v>
+        <v>0.0183</v>
       </c>
       <c r="X5" s="2">
-        <v>0.0199</v>
+        <v>0.0091</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0413</v>
+        <v>0.0303</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.089</v>
+        <v>0.0775</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.3038</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>940.3</v>
+        <v>934.4</v>
       </c>
       <c r="D6" s="1">
-        <v>0.6</v>
+        <v>-5.3</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0006</v>
+        <v>-0.0056</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-33.4</v>
+        <v>-39.3</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0343</v>
+        <v>-0.0404</v>
       </c>
       <c r="L6" s="1">
-        <v>-33.4</v>
+        <v>-39.3</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0343</v>
+        <v>-0.0404</v>
       </c>
       <c r="N6" s="1">
-        <v>4</v>
+        <v>-1.9</v>
       </c>
       <c r="O6" s="1">
-        <v>4.1</v>
+        <v>-1.9</v>
       </c>
       <c r="P6" s="1">
-        <v>-33.3</v>
+        <v>-39.3</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0323</v>
+        <v>0.0321</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>16</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0006</v>
+        <v>-0.0056</v>
       </c>
       <c r="U6" s="5">
-        <v>9.403</v>
+        <v>9.344</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0355</v>
+        <v>0.0421</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0284</v>
+        <v>-0.0345</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.14</v>
+        <v>-0.1453</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0371</v>
+        <v>0.0306</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.276</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="7">
@@ -947,49 +947,49 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3029.4</v>
+        <v>3032.1</v>
       </c>
       <c r="D7" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.0009</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" s="2">
+        <v/>
+      </c>
+      <c r="H7" s="1">
+        <v/>
+      </c>
+      <c r="I7" s="2">
+        <v/>
+      </c>
+      <c r="J7" s="1">
+        <v>13.35</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0.0044</v>
+      </c>
+      <c r="L7" s="1">
+        <v>13.35</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0.0044</v>
+      </c>
+      <c r="N7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="2">
+      <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" s="2">
-        <v/>
-      </c>
-      <c r="H7" s="1">
-        <v/>
-      </c>
-      <c r="I7" s="2">
-        <v/>
-      </c>
-      <c r="J7" s="1">
-        <v>10.65</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.0035</v>
-      </c>
-      <c r="L7" s="1">
-        <v>10.65</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.0035</v>
-      </c>
-      <c r="N7" s="1">
-        <v>-2.7</v>
-      </c>
-      <c r="O7" s="1">
-        <v>-2.7</v>
-      </c>
       <c r="P7" s="1">
-        <v>10.65</v>
+        <v>13.35</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.104</v>
+        <v>0.1042</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>16</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>0.0009</v>
       </c>
       <c r="U7" s="5">
-        <v>1.122</v>
+        <v>1.123</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0045</v>
+        <v>0.0054</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0126</v>
+        <v>0.0135</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0154</v>
+        <v>0.0163</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0225</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>809.6</v>
+        <v>792.8</v>
       </c>
       <c r="D8" s="1">
-        <v>-1</v>
+        <v>-17.8</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0012</v>
+        <v>-0.022</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,28 +1051,28 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="K8" s="2">
-        <v>0.0291</v>
+        <v>0.0078</v>
       </c>
       <c r="L8" s="1">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="M8" s="2">
-        <v>0.0291</v>
+        <v>0.0078</v>
       </c>
       <c r="N8" s="1">
-        <v>-23</v>
+        <v>-39.6</v>
       </c>
       <c r="O8" s="1">
-        <v>-22.8</v>
+        <v>-39.6</v>
       </c>
       <c r="P8" s="1">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.0278</v>
+        <v>0.0272</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -1081,10 +1081,10 @@
         <v>16</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0012</v>
+        <v>-0.022</v>
       </c>
       <c r="U8" s="5">
-        <v>4.048</v>
+        <v>3.964</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
@@ -1093,16 +1093,16 @@
         <v/>
       </c>
       <c r="X8" s="2">
-        <v>0.0973</v>
+        <v>0.0746</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.2263</v>
+        <v>0.2008</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.3338</v>
+        <v>0.3061</v>
       </c>
       <c r="AA8" s="2">
-        <v>1.0528</v>
+        <v>1.0102</v>
       </c>
     </row>
     <row r="9">
@@ -1146,7 +1146,7 @@
         <v>-0.0356</v>
       </c>
       <c r="N9" s="1">
-        <v>-137.2</v>
+        <v>-149.8</v>
       </c>
       <c r="O9" s="1">
         <v>-149.8</v>
@@ -1155,7 +1155,7 @@
         <v>-725.84</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6743</v>
+        <v>0.6752</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1196,13 +1196,13 @@
         <v>能源化工</v>
       </c>
       <c r="C10" s="1">
-        <v>644.4</v>
+        <v>647.2</v>
       </c>
       <c r="D10" s="1">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E10" s="2">
-        <v>0.0164</v>
+        <v>0.0208</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1217,28 +1217,28 @@
         <v/>
       </c>
       <c r="J10" s="1">
-        <v>-27.7</v>
+        <v>-24.9</v>
       </c>
       <c r="K10" s="2">
-        <v>-0.0412</v>
+        <v>-0.0371</v>
       </c>
       <c r="L10" s="1">
-        <v>-27.7</v>
+        <v>-24.9</v>
       </c>
       <c r="M10" s="2">
-        <v>-0.0412</v>
+        <v>-0.0371</v>
       </c>
       <c r="N10" s="1">
-        <v>9.2</v>
+        <v>12</v>
       </c>
       <c r="O10" s="1">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="P10" s="1">
-        <v>-27.3</v>
+        <v>-24.9</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0221</v>
+        <v>0.0222</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1247,28 +1247,28 @@
         <v>16</v>
       </c>
       <c r="T10" s="2">
-        <v>0.0164</v>
+        <v>0.0208</v>
       </c>
       <c r="U10" s="5">
-        <v>1.611</v>
+        <v>1.618</v>
       </c>
       <c r="V10" s="5">
         <v>1.68</v>
       </c>
       <c r="W10" s="2">
-        <v>0.0428</v>
+        <v>0.0383</v>
       </c>
       <c r="X10" s="2">
-        <v>-0.0661</v>
+        <v>-0.0621</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.2605</v>
+        <v>0.266</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.3055</v>
+        <v>0.3111</v>
       </c>
       <c r="AA10" s="2">
-        <v>0.2566</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="11">
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>860</v>
+        <v>859.6</v>
       </c>
       <c r="D11" s="1">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,25 +1300,25 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0006</v>
+        <v>-0.001</v>
       </c>
       <c r="L11" s="1">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0006</v>
+        <v>-0.001</v>
       </c>
       <c r="N11" s="1">
-        <v>-2.4</v>
+        <v>-3.6</v>
       </c>
       <c r="O11" s="1">
-        <v>-2.4</v>
+        <v>-3.6</v>
       </c>
       <c r="P11" s="1">
-        <v>0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="Q11" s="2">
         <v>0.0295</v>
@@ -1330,28 +1330,28 @@
         <v>16</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="U11" s="5">
-        <v>2.15</v>
+        <v>2.149</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0005</v>
+        <v>0.0009</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0312</v>
+        <v>0.0307</v>
       </c>
       <c r="Y11" s="2">
-        <v>-0.0069</v>
+        <v>-0.0074</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.18</v>
+        <v>0.1795</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.2967</v>
+        <v>0.2961</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29141.9</v>
+        <v>29105.3</v>
       </c>
       <c r="D12" s="1">
-        <v>73.7</v>
+        <v>37.1</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0025</v>
+        <v>0.0013</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-849.89</v>
+        <v>-886.49</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.0283</v>
+        <v>-0.0296</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-178.9</v>
+        <v>-227.9</v>
       </c>
       <c r="O12" s="1">
-        <v>-189.2</v>
+        <v>-227.9</v>
       </c>
       <c r="P12" s="1">
-        <v>-847.79</v>
+        <v>-886.49</v>
       </c>
       <c r="Q12" s="2">
         <v>1</v>
